--- a/templates/SPA/country_data.xlsx
+++ b/templates/SPA/country_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f5aee5c5b004427f/Documents/mr-risk-assessment/templates/SPA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{8A19CEE9-D290-A84C-A865-FBE6391B7508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0489172E-E65D-4800-8754-C30B3D7F32E8}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{8A19CEE9-D290-A84C-A865-FBE6391B7508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7622AE8-7758-4C8D-8B8E-613FC1665189}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="380" windowWidth="19180" windowHeight="10060" tabRatio="773" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="773" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-General" sheetId="1" r:id="rId1"/>
@@ -684,7 +684,7 @@
     <t>SPA</t>
   </si>
   <si>
-    <t>El equipo subnacional de respuesta rápida fue entrenado en los últimos 2 años</t>
+    <t>El equipo subnacional de respuesta rápida fue entrenado en los últimos 2 años (Si/No)</t>
   </si>
 </sst>
 </file>
@@ -4672,6 +4672,12 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007C69FE739999C447A76F1EF8B3FD66E4" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="cbd048430c8551c34c2c3c8571f1b260">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="4655c133-e14e-4d88-8fbc-c3b347145ec5" xmlns:ns4="64ced670-a384-4657-ba0f-fc07d30f5a44" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5457dbb80d17598a17de4d439e456cf2" ns3:_="" ns4:_="">
     <xsd:import namespace="4655c133-e14e-4d88-8fbc-c3b347145ec5"/>
@@ -4894,12 +4900,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6264E33-6917-4678-8EC8-8D88A2F9795C}">
   <ds:schemaRefs>
@@ -4909,6 +4909,23 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A51E5E2-41F2-4A1F-A4B0-950DEDB4B143}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="4655c133-e14e-4d88-8fbc-c3b347145ec5"/>
+    <ds:schemaRef ds:uri="64ced670-a384-4657-ba0f-fc07d30f5a44"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1C9E008-75C3-4280-8CCC-7498B59407BC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4925,21 +4942,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A51E5E2-41F2-4A1F-A4B0-950DEDB4B143}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="4655c133-e14e-4d88-8fbc-c3b347145ec5"/>
-    <ds:schemaRef ds:uri="64ced670-a384-4657-ba0f-fc07d30f5a44"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>